--- a/E/ADP01D.xlsx
+++ b/E/ADP01D.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
   <si>
     <t/>
   </si>
   <si>
-    <t>20137683</t>
-  </si>
-  <si>
-    <t>CONF D.FRSH PANTS M9</t>
+    <t>20130829</t>
+  </si>
+  <si>
+    <t>CONF.ADLT PNT ES 10M</t>
   </si>
   <si>
     <t>ADP01D</t>
@@ -28,39 +28,33 @@
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20130830</t>
+  </si>
+  <si>
+    <t>CONF.ADLT PANT ES 8L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20136042</t>
+  </si>
+  <si>
+    <t>CONF.ADL PNT ES XL/6</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20130829</t>
-  </si>
-  <si>
-    <t>CONF.ADLT PNT ES 10M</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20130830</t>
-  </si>
-  <si>
-    <t>CONF.ADLT PANT ES 8L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20136042</t>
-  </si>
-  <si>
-    <t>CONF.ADL PNT ES XL/6</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20139327</t>
   </si>
   <si>
@@ -77,12 +71,6 @@
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>20137682</t>
-  </si>
-  <si>
-    <t>CONF D.FRSH PANTS L8</t>
   </si>
   <si>
     <t>20065463</t>
@@ -631,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -675,18 +663,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -695,10 +683,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -718,15 +706,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -735,18 +723,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -755,30 +743,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -792,13 +780,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -812,13 +800,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,153 +820,153 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -992,21 +980,21 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1015,18 +1003,18 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1035,10 +1023,10 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1052,13 +1040,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1072,13 +1060,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1092,13 +1080,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,13 +1100,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,53 +1120,53 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,13 +1180,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1212,53 +1200,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/ADP01D.xlsx
+++ b/E/ADP01D.xlsx
@@ -11,48 +11,108 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t/>
   </si>
   <si>
+    <t>20130828</t>
+  </si>
+  <si>
+    <t>CONF.ADLT PANT TP 8L</t>
+  </si>
+  <si>
+    <t>ADP01D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142330</t>
+  </si>
+  <si>
+    <t>CONFIDENCE TIPIS XL6</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137862</t>
+  </si>
+  <si>
+    <t>CERTAINTY PANTS M-8S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137863</t>
+  </si>
+  <si>
+    <t>CERTAINTY PANTS L-7S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20090847</t>
+  </si>
+  <si>
+    <t>CERTAINTY POPOK 8S/M</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20090848</t>
+  </si>
+  <si>
+    <t>CERTAINTY POPOK 7S/L</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20108877</t>
+  </si>
+  <si>
+    <t>LIFREE PANT LGH 6 XL</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20130829</t>
   </si>
   <si>
     <t>CONF.ADLT PNT ES 10M</t>
   </si>
   <si>
-    <t>ADP01D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20130830</t>
   </si>
   <si>
     <t>CONF.ADLT PANT ES 8L</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>20136042</t>
   </si>
   <si>
     <t>CONF.ADL PNT ES XL/6</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>20139328</t>
+  </si>
+  <si>
+    <t>HAPPILY PANTS M10</t>
   </si>
   <si>
     <t>20139327</t>
@@ -61,16 +121,43 @@
     <t>HAPPILY PANTS L8</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139328</t>
-  </si>
-  <si>
-    <t>HAPPILY PANTS M10</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>20065462</t>
+  </si>
+  <si>
+    <t>CONF.ADLT DIAPRS 6XL</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20108875</t>
+  </si>
+  <si>
+    <t>LIFREE PANT LGH 10 M</t>
+  </si>
+  <si>
+    <t>20093913</t>
+  </si>
+  <si>
+    <t>LIFREE PANT LGH 8S L</t>
+  </si>
+  <si>
+    <t>20045615</t>
+  </si>
+  <si>
+    <t>LIFREE PPK PRKT 8S M</t>
+  </si>
+  <si>
+    <t>20045621</t>
+  </si>
+  <si>
+    <t>LIFREE PPK PRKT 7S L</t>
+  </si>
+  <si>
+    <t>20065464</t>
+  </si>
+  <si>
+    <t>CONF.ADLT DIAP.CLS8M</t>
   </si>
   <si>
     <t>20065463</t>
@@ -79,33 +166,6 @@
     <t>CONF.ADLT DIAP.CLS7L</t>
   </si>
   <si>
-    <t>20065462</t>
-  </si>
-  <si>
-    <t>CONF.ADLT DIAPRS 6XL</t>
-  </si>
-  <si>
-    <t>20065464</t>
-  </si>
-  <si>
-    <t>CONF.ADLT DIAP.CLS8M</t>
-  </si>
-  <si>
-    <t>20137862</t>
-  </si>
-  <si>
-    <t>CERTAINTY PANTS M-8S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137863</t>
-  </si>
-  <si>
-    <t>CERTAINTY PANTS L-7S</t>
-  </si>
-  <si>
     <t>20070687</t>
   </si>
   <si>
@@ -121,6 +181,12 @@
     <t>LIFREE PPK CLN 8S L</t>
   </si>
   <si>
+    <t>20070688</t>
+  </si>
+  <si>
+    <t>LIFREE PPK CLN 6 XL</t>
+  </si>
+  <si>
     <t>20124631</t>
   </si>
   <si>
@@ -130,103 +196,49 @@
     <t>PT,(E-4B)</t>
   </si>
   <si>
-    <t>20045621</t>
-  </si>
-  <si>
-    <t>LIFREE PPK PRKT 7S L</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20045615</t>
-  </si>
-  <si>
-    <t>LIFREE PPK PRKT 8S M</t>
-  </si>
-  <si>
-    <t>20090848</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 7S/L</t>
-  </si>
-  <si>
-    <t>20090847</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 8S/M</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20070688</t>
-  </si>
-  <si>
-    <t>LIFREE PPK CLN 6 XL</t>
-  </si>
-  <si>
-    <t>20108877</t>
-  </si>
-  <si>
-    <t>LIFREE PANT LGH 6 XL</t>
-  </si>
-  <si>
-    <t>20108875</t>
-  </si>
-  <si>
-    <t>LIFREE PANT LGH 10 M</t>
-  </si>
-  <si>
     <t>20056799</t>
   </si>
   <si>
     <t>LIFREE PPK PRKT 6 XL</t>
   </si>
   <si>
-    <t>20093913</t>
-  </si>
-  <si>
-    <t>LIFREE PANT LGH 8S L</t>
-  </si>
-  <si>
     <t>20069549</t>
   </si>
   <si>
     <t>IDM DIAPER ADULT 6XL</t>
   </si>
   <si>
+    <t>20127694</t>
+  </si>
+  <si>
+    <t>LARSST PANTS ADL 10M</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20127573</t>
+  </si>
+  <si>
+    <t>LARISST PANTS ADL 8L</t>
+  </si>
+  <si>
     <t>20127575</t>
   </si>
   <si>
     <t>LARISST PANTS ADL6XL</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20127573</t>
-  </si>
-  <si>
-    <t>LARISST PANTS ADL 8L</t>
-  </si>
-  <si>
-    <t>20127694</t>
-  </si>
-  <si>
-    <t>LARSST PANTS ADL 10M</t>
+    <t>20069546</t>
+  </si>
+  <si>
+    <t>IDM DIAPER ADULT 8M</t>
   </si>
   <si>
     <t>20069547</t>
   </si>
   <si>
     <t>IDM DIAPER ADULT 7L</t>
-  </si>
-  <si>
-    <t>20069546</t>
-  </si>
-  <si>
-    <t>IDM DIAPER ADULT 8M</t>
   </si>
 </sst>
 </file>
@@ -619,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -663,18 +675,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -683,10 +695,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,10 +772,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
@@ -771,102 +783,102 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -880,13 +892,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,13 +912,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,81 +932,81 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1003,18 +1015,18 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1023,90 +1035,90 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1123,18 +1135,18 @@
         <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1143,30 +1155,30 @@
         <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1180,13 +1192,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1200,13 +1212,53 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>13</v>
+      <c r="F30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
